--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_aamas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/366149424dfc0f64/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208DF7E0-118C-4694-BE52-4EC829B00D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{208DF7E0-118C-4694-BE52-4EC829B00D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0427190C-634E-450B-9764-0367BD3A8DDC}"/>
   <bookViews>
-    <workbookView xWindow="5955" yWindow="5250" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2715" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grilla" sheetId="1" r:id="rId1"/>
@@ -3292,13 +3292,13 @@
         <v>228076.1</v>
       </c>
       <c r="E110">
-        <v>186316.54</v>
+        <v>183802.56</v>
       </c>
       <c r="F110">
-        <v>143210.6</v>
+        <v>140613.07999999999</v>
       </c>
       <c r="G110">
-        <v>122775.9</v>
+        <v>120056.76</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -3315,13 +3315,13 @@
         <v>235433.39</v>
       </c>
       <c r="E111">
-        <v>192326.76</v>
+        <v>189731.67</v>
       </c>
       <c r="F111">
-        <v>147830.29</v>
+        <v>145148.99</v>
       </c>
       <c r="G111">
-        <v>126736.42</v>
+        <v>123929.56</v>
       </c>
     </row>
   </sheetData>
